--- a/dados/enviadas/Cabala.xlsx
+++ b/dados/enviadas/Cabala.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$I$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -451,18 +451,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="59" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="59" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,35 +479,40 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>ITEM</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>MODALIDADE</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>VALOR_ESTIMADO</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>ORGAO</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>DATA_DISPUTA</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>PORTAL</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>LINK_PORTAL</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>LINK_PNCP</t>
         </is>
@@ -520,40 +526,41 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>PE 015/2026</t>
+          <t>102/2026</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>11571015</v>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE ITABERABA</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>27/08/2026</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>BLL</t>
+          <t>Veículos diversos</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>1981118.35</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE CAMPO GRANDE</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>https://bllcompras.com/Process/ProcessView?param1=[gkz]cXM2M1XTkBZxOhjDXwRVOP9hA9p/EaYj1LJYD5CxhEpIopfQ_6R7/aTONeQmC1Tp4N5QxmQkNhM1IakDZsS4uszonxLC_tblRaKGXixIUwk=</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/13719646000175/2026/134</t>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/03501509000106/2026/102</t>
         </is>
       </c>
     </row>
@@ -565,40 +572,45 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>073/2026</t>
+          <t>027/2026</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>4441662.87</v>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE PONTE NOVA</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>24/08/2026</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Licitar Digital</t>
+          <t>Veículos diversos</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>417483.27</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE BELEM DE SAO FRANCISCO</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>https://app2.licitardigital.com.br/pesquisa/109757</t>
+          <t>Portal de Compras Públicas</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://pncp.gov.br/app/editais/23804149000129/2026/309</t>
+          <t>https://www.portaldecompraspublicas.com.br/processos/PE/Prefeitura-Municipal-de-Belem-de-Sao-Francisco-4988/PE-027-2026-2026-514041</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/10113728000183/2026/53</t>
         </is>
       </c>
     </row>
@@ -610,45 +622,464 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>0034/2026</t>
+          <t>(9217) | 21-0/2026</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>539000</v>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE CAPELINHA</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>24/08/2026</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Licitar Digital</t>
+          <t>Veículos diversos</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>399612.8</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>FUNDO MUNICIPAL DE SAUDE DE ARUANA</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>https://app2.licitardigital.com.br/pesquisa/110083</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/19229921000159/2026/75</t>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/12213549000143/2026/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Cabala</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>048/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Veículos diversos</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>957000</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE BOM JESUS DA LAPA</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>BNC Compras</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://bnccompras.com/Process/ProcessView?param1=[gkz]Wh2eCuasAKovrf8IxtUETOteWo6ofcSKPIc5MYcB0pS_IHJFaUoyPtO69S5g_PCVMeSGMZ/cm8v_qmeSMKYia3Gpde9JJ51eB3od2tTCf6s=</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/14105183000114/2026/138</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Cabala</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>27/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>2162000</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE BURITIS</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>AMM Licita</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>https://app2.ammlicita.org.br/pesquisa/113754</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/18125146000129/2026/75</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Cabala</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>240/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Veículos diversos</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>347633.33</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>BOM JESUS DO ITABAPOANA PREFEITURA</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>ComprasGov</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://cnetmobile.estaleiro.serpro.gov.br/comprasnet-web/public/compras/acompanhamento-compra?compra=98581105002402026</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/29112760000172/2026/275</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Cabala</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>195/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Veículos diversos</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>822264.05</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE VOLTA REDONDA</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>ComprasGov</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>https://cnetmobile.estaleiro.serpro.gov.br/comprasnet-web/public/compras/acompanhamento-compra?compra=45006805001952026</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/32512501000143/2026/348</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Cabala</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>20/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Veículos diversos</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>53214168</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>CONSORCIO INTERMUNICIPAL DO VALE DO PARANAPANEMA</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/51501484000193/2026/41</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Cabala</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>55/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Veículos diversos</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>336749.08</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE MATELANDIA</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/76206465000165/2026/153</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Cabala</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>PE 25/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Veículos diversos</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>4142165.57</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE JAGUARIAIVA</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/76910900000138/2026/55</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Cabala</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>068/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Veículos diversos</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>1657629.5</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE ITURAMA</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Licitanet</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>https://licitanet.com.br/sessao/197624</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/18457242000174/2026/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Cabala</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>42/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Veículos diversos</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>2848026.68</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE ESPERANCA</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Portal de Compras Públicas</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.portaldecompraspublicas.com.br/processos/PB/Prefeitura-Municipal-de-Esperanca-1305/RPE-42-2026-2026-514509</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/08993909000108/2026/156</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I4"/>
+  <autoFilter ref="A1:J13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/dados/enviadas/Cabala.xlsx
+++ b/dados/enviadas/Cabala.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,9 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[$R$-416] #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="[$R$-416] #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="DD/MM/YYYY"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -69,21 +70,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -451,635 +453,403 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="59" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>CLIENTE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>ITEM</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>MODALIDADE</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>VALOR_ESTIMADO</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>ORGAO</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>DATA_DISPUTA</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>PORTAL</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>LINK_PORTAL</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>LINK_PNCP</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Cabala</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>102/2026</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>024/2026</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Veículos diversos</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Pregão - Eletrônico</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>1981118.35</v>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE CAMPO GRANDE</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr"/>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/03501509000106/2026/102</t>
+      <c r="E2" s="5" t="n">
+        <v>2645703.84</v>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE CAPIM GROSSO</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>46315.39583333334</v>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Licitanet</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>https://licitanet.com.br/sessao/201096</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/13230982000150/2026/168</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Cabala</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>027/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>039/2026</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Veículos diversos</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Pregão - Eletrônico</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n">
-        <v>417483.27</v>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE BELEM DE SAO FRANCISCO</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>08/10/2026</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Portal de Compras Públicas</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.portaldecompraspublicas.com.br/processos/PE/Prefeitura-Municipal-de-Belem-de-Sao-Francisco-4988/PE-027-2026-2026-514041</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/10113728000183/2026/53</t>
+      <c r="E3" s="5" t="n">
+        <v>1851646.33</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE ALTO JEQUITIBA</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>46308.52083333334</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>AMM Licita</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>https://app2.ammlicita.org.br/pesquisa/115039</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/18392506000159/2026/114</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Cabala</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>(9217) | 21-0/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>26/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Veículos diversos</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Pregão - Eletrônico</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>399612.8</v>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>FUNDO MUNICIPAL DE SAUDE DE ARUANA</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/12213549000143/2026/5</t>
+      <c r="E4" s="5" t="n">
+        <v>553419.33</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE FORMOSO DO ARAGUAIA</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>46304.33263888889</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Portal de Compras Públicas</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.portaldecompraspublicas.com.br/processos/TO/Prefeitura-Municipal-de-Formoso-do-Araguaia-1369/PE-26-2026-2026-514861</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/02075216000141/2026/37</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Cabala</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>048/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>14/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Veículos diversos</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Pregão - Eletrônico</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>957000</v>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE BOM JESUS DA LAPA</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>08/10/2026</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>BNC Compras</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>https://bnccompras.com/Process/ProcessView?param1=[gkz]Wh2eCuasAKovrf8IxtUETOteWo6ofcSKPIc5MYcB0pS_IHJFaUoyPtO69S5g_PCVMeSGMZ/cm8v_qmeSMKYia3Gpde9JJ51eB3od2tTCf6s=</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/14105183000114/2026/138</t>
+      <c r="E5" s="5" t="n">
+        <v>22105866.83</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>CONSORCIO INTERMUNICIPAL MULTIFINALITARIO DOS MUNICIPIOS DA AMNAP - CIM AMNAP</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>46310.35416666666</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/45129177000120/2026/12</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Cabala</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>27/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>1062/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Vans</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Pregão - Eletrônico</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>2162000</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE BURITIS</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>02/10/2026</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>AMM Licita</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>https://app2.ammlicita.org.br/pesquisa/113754</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/18125146000129/2026/75</t>
+      <c r="E6" s="5" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE FEDERAL DE UBERLANDIA</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>46308.375</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>ComprasGov</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>https://cnetmobile.estaleiro.serpro.gov.br/comprasnet-web/public/compras/acompanhamento-compra?compra=15404305010622026</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/25648387000118/2026/195</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Cabala</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>240/2026</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Veículos diversos</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>PCE 39/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Pregão - Eletrônico</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>347633.33</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>BOM JESUS DO ITABAPOANA PREFEITURA</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>ComprasGov</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>https://cnetmobile.estaleiro.serpro.gov.br/comprasnet-web/public/compras/acompanhamento-compra?compra=98581105002402026</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/29112760000172/2026/275</t>
+      <c r="E7" s="5" t="n">
+        <v>358450</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE SUMARE</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>46308.37430555555</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/45787660000100/2026/268</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Cabala</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>195/2026</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Veículos diversos</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>43/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Pregão - Eletrônico</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>822264.05</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE VOLTA REDONDA</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>ComprasGov</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>https://cnetmobile.estaleiro.serpro.gov.br/comprasnet-web/public/compras/acompanhamento-compra?compra=45006805001952026</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/32512501000143/2026/348</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Cabala</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>20/2026</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Veículos diversos</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>53214168</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>CONSORCIO INTERMUNICIPAL DO VALE DO PARANAPANEMA</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/51501484000193/2026/41</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Cabala</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>55/2026</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Veículos diversos</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>336749.08</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE MATELANDIA</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>09/10/2026</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/76206465000165/2026/153</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Cabala</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>PE 25/2026</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Veículos diversos</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>4142165.57</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE JAGUARIAIVA</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/76910900000138/2026/55</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Cabala</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>068/2026</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Veículos diversos</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>1657629.5</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE ITURAMA</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Licitanet</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>https://licitanet.com.br/sessao/197624</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/18457242000174/2026/50</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Cabala</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>42/2026</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Veículos diversos</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>2848026.68</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE ESPERANCA</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Portal de Compras Públicas</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>https://www.portaldecompraspublicas.com.br/processos/PB/Prefeitura-Municipal-de-Esperanca-1305/RPE-42-2026-2026-514509</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/08993909000108/2026/156</t>
+      <c r="E8" s="5" t="n">
+        <v>810449.59</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE PRESIDENTE PRUDENTE</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>46310.5625</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Licitar Digital</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>https://app2.licitardigital.com.br/pesquisa/115128</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>https://pncp.gov.br/app/editais/55356653000108/2026/248</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J13"/>
+  <autoFilter ref="A1:J8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>